--- a/business_forms/037_white_label_product_batch_order_form--business_forms.xlsx
+++ b/business_forms/037_white_label_product_batch_order_form--business_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>payment_info</t>
+          <t>payment_info_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Payment Information</t>
+          <t>Payment Info 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>order_confirmation</t>
+          <t>order_confirmation_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Order Confirmation</t>
+          <t>Order Confirmation 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>review_confirmation</t>
+          <t>review_confirmation_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Review Confirmation</t>
+          <t>Review Confirmation 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>payment_info</t>
+          <t>payment_info_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Payment Information</t>
+          <t>Payment Info 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>payment_confirmation</t>
+          <t>payment_confirmation_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Payment Confirmation</t>
+          <t>Payment Confirmation 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>review_info</t>
+          <t>review_info_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Review and Approval</t>
+          <t>Review Info 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
